--- a/VAVILOV2_PIPELINE_DESCRIPTION.xlsx
+++ b/VAVILOV2_PIPELINE_DESCRIPTION.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROGRAMAS\Dropbox\VAVILOV_2.0\Results\SUMMARY_FILES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO_GITHUB\VAVILOV_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF134AB-3F2B-47FC-BE12-7B25047D4119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75812B23-D826-46C3-9EC8-16894F36E5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="800" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Preprocessing Pipeline" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,9 @@
     <sheet name="3.CONCAVE_HULL" sheetId="4" r:id="rId4"/>
     <sheet name="4.potential_realized_niche" sheetId="6" r:id="rId5"/>
     <sheet name="5.Soil_outliers" sheetId="7" r:id="rId6"/>
-    <sheet name="6.STATS" sheetId="9" r:id="rId7"/>
+    <sheet name="6.Category_maps" sheetId="13" r:id="rId7"/>
+    <sheet name="7.STATS" sheetId="9" r:id="rId8"/>
+    <sheet name="8.Extra_Steps" sheetId="15" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="165">
   <si>
     <t>Step</t>
   </si>
@@ -523,12 +525,99 @@
 • 'summary_growth_form_Engemann.png' — species count by growth form
 • 'summary_growth_plant_cultivated_status.png' — species count by cultivated status</t>
   </si>
+  <si>
+    <t>Master</t>
+  </si>
+  <si>
+    <t>main_summary_richess_categories.R</t>
+  </si>
+  <si>
+    <t>scriptdir = .../4.Scripts/TO_DOCUMENT/4.Scripts/006_category_maps; basedir = D:/PROGRAMAS/Dropbox/VAVILOV_2.0</t>
+  </si>
+  <si>
+    <t>Orchestrator script. Sets the working user/directory, then opens (via file.edit) each of the four richness scripts in sequence for interactive editing/execution: potential distribution (Step 1), realized distribution (Step 2), future potential distribution (Step 3), and future realized distribution (Step 4). Does not itself run any computation - it is a navigation/documentation aid pointing to the correct scripts and folder (006_category_maps).</t>
+  </si>
+  <si>
+    <t>None (opens the four scripts listed in Steps 1-4 for editing/running)</t>
+  </si>
+  <si>
+    <t>001_summary_Richness_categories_potential.R</t>
+  </si>
+  <si>
+    <t>species_selected (curated edible-part xlsx); AUC_Maxent_valid.csv (valid SDM models); presence-absence rasters per species (Distribution maps/Presence-absence); buffer rasters per species (buffer_richness/raster); climate template raster (wc2.1_2.5m_bio_1.tif); adm0_Latam shapefile</t>
+  </si>
+  <si>
+    <t>For each category within a chosen column (plant_part, food_group, cultivated, wild), splits species into SDM-modeled vs. buffer-only. Sums presence rasters in parallel chunks (foreach %dopar%, chunks of 10) to get SDM richness and buffer richness per category, combines both sources (potential distribution, unmasked), resamples to template, and produces a PNG map (with adm0 outline) and an interactive Leaflet HTML map with quantile-based color bins.</t>
+  </si>
+  <si>
+    <t>SDM_richness_current.tif, buffer_richness_current.tif, richness_current.tif (per category), PNG maps, HTML maps - under Summary_maps_categories/{TIF,PNG,HTML}</t>
+  </si>
+  <si>
+    <t>002_summary_Richness_categories_concave.R</t>
+  </si>
+  <si>
+    <t>species_selected (xlsx); AUC_Maxent_valid_ALL.csv; concave-hull-masked rasters (TIF_ConcaveHull, already unifying modeled and buffer species); climate template raster; adm0_Latam shapefile</t>
+  </si>
+  <si>
+    <t>Same category loop and parallel chunked summation as Step 1, but sums the already concave-hull-masked ("realized") rasters instead of raw potential ones. No separate SDM/buffer combination step is needed since both are unified in the ConcaveHull folder. Produces current realized richness per category, with PNG and Leaflet HTML outputs.</t>
+  </si>
+  <si>
+    <t>richness_current.tif (realized, per category), PNG maps, HTML maps - under Summary_maps_categories_realized/{TIF,PNG,HTML}</t>
+  </si>
+  <si>
+    <t>003_summary_Richness_categories_final_climate_change.R</t>
+  </si>
+  <si>
+    <t>species_selected (xlsx); AUC_Maxent_valid_ALL.csv + AUC_Maxent_warning.csv (valid + warning models combined); future consensus SDM rasters, no hull (Fut_consensus/NO_HULL, 2050, ssp245/ssp370); climate template raster; adm0_Latam shapefile</t>
+  </si>
+  <si>
+    <t>Double loop: SSP (245, 370) x category. For each species, thresholds the GCM consensus raster (&gt;=3 GCMs agreeing -&gt; 1/0) and sums in parallel chunks to obtain future potential richness per category and scenario. Produces PNG and Leaflet HTML outputs per SSP.</t>
+  </si>
+  <si>
+    <t>SDM_richness_future_ssp245.tif / _ssp370.tif (per category), PNG maps, HTML maps - under Summary_maps_categories/{TIF_future,PNG_future,HTML_future}</t>
+  </si>
+  <si>
+    <t>004_summary_Richness_categories_final_climate_change_realized.R</t>
+  </si>
+  <si>
+    <t>species_selected (xlsx); AUC_Maxent_valid_ALL.csv + AUC_Maxent_warning.csv; future concave-hull-masked rasters (Summary_maps_folder_CC/TIF_SP_REALIZED_SDM/ConcaveHull); climate template raster; adm0_Latam shapefile</t>
+  </si>
+  <si>
+    <t>Same SSP x category double loop as Step 3, but sums the future concave-hull-masked ("realized") rasters instead of the raw consensus ones. Produces future realized richness per category and scenario, with PNG and Leaflet HTML outputs.</t>
+  </si>
+  <si>
+    <t>SDM_richness_future_ssp245.tif / _ssp370.tif (realized, per category), PNG maps, HTML maps - under Summary_maps_categories/{TIF_future_realized,PNG_future_realized,HTML_future_realized}</t>
+  </si>
+  <si>
+    <t>000_COPY_TO_D4N.R</t>
+  </si>
+  <si>
+    <t>species_selected (curated edible-part xlsx); AUC_Maxent_valid_all.csv (valid SDM models); PROJECT_STATUS.xlsx (synonym/conversion table); current presence-absence rasters per species (Distribution maps/Presence-absence); buffer rasters per species (buffer_richness/raster); future consensus rasters (Fut_consensus/NO_HULL, ssp245/ssp370); concave-hull rasters per species (concave_hull_rasters_ADM0_2_5m)</t>
+  </si>
+  <si>
+    <t>For every species, checks whether it has a valid SDM model; if not, looks up an accepted-name synonym via the conversion table and re-checks. Loads the species' concave hull (native range mask) if available. Copies (or masks/resamples then writes) each species' raster into a consolidated D4N_data folder structure, for four combinations: current potential, current realized (masked by concave hull), future SSP2/SSP3 potential, and future SSP2/SSP3 realized (resampled and masked by concave hull). Falls back to buffer rasters when no SDM model exists, and to the synonym's files when the accepted name has no direct match.</t>
+  </si>
+  <si>
+    <t>Per-species .tif files copied into D4N_data/{Presence-absence, Presence-absence masked by hull, Future/SSP2, Future/SSP3, Future masked by hull/SSP2, Future masked by hull/SSP3} - a consolidated, one-file-per-species data delivery folder ("D4N")</t>
+  </si>
+  <si>
+    <t>FIGURE_FOR_PAPER.R</t>
+  </si>
+  <si>
+    <t>None (synthetic data generated in-script with set.seed(42) via rnorm())</t>
+  </si>
+  <si>
+    <t>Standalone, self-contained script (not part of the species/category pipeline) that builds a conceptual two-panel illustrative figure for a paper. Panel 1 simulates an ecosystem distribution and a species distribution where the species' 10th percentile exceeds the ecosystem's 90th percentile; Panel 2 simulates the opposite case (ecosystem 10th percentile exceeds species 90th percentile). Each panel plots overlapping density curves with dashed quantile reference lines and labelled annotations, using fixed shared x/y axis limits for visual alignment. Panels are combined vertically with patchwork, given a shared legend and title, displayed in the session, and exported as a high-resolution PNG.</t>
+  </si>
+  <si>
+    <t>quantile_comparison_panel.png (1000 DPI, 12x10 in) saved to D:/PROGRAMAS/Dropbox/VAVILOV_2.0/Results/SUMMARY_FILES</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -554,8 +643,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F4E5F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -583,8 +699,14 @@
         <bgColor rgb="FFF2F5F8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F6F8"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -622,11 +744,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7C4CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7C4CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7C4CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7C4CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -655,9 +793,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{3418E251-D7DF-4F51-A31A-86F1A5255C92}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1590,6 +1745,125 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0449FDE8-6961-4245-A3B3-7B6ACB8BCD7E}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="191.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68.21875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="255.77734375" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="189" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="11.5546875" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="191.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="191.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="191.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="191.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="191.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="191.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
+        <v>4</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD741F23-D3A9-44CC-BF15-8D3DC4680605}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1631,4 +1905,65 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB14A99-676D-49D2-81D8-66AD500FE844}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>